--- a/02_Basic_Excel_for_Data_Analytics/20A_Workbook-Reference-2.xlsx
+++ b/02_Basic_Excel_for_Data_Analytics/20A_Workbook-Reference-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 COURSES\Learn_Data_Analytics_by_CWH\02_Basic_Excel_for_Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748E3112-EEBB-4E90-8936-3E00DB0ACC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B913A352-26D6-45C3-82E5-A8F083C653EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -414,7 +414,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
